--- a/artfynd/A 25651-2025 artfynd.xlsx
+++ b/artfynd/A 25651-2025 artfynd.xlsx
@@ -1184,7 +1184,7 @@
         <v>127122269</v>
       </c>
       <c r="B6" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>127122952</v>
       </c>
       <c r="B8" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1529,38 +1529,38 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127122563</v>
+        <v>127122519</v>
       </c>
       <c r="B9" t="n">
-        <v>5176</v>
+        <v>57817</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100526</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1569,13 +1569,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>654600</v>
+        <v>654594</v>
       </c>
       <c r="R9" t="n">
-        <v>6648068</v>
+        <v>6648065</v>
       </c>
       <c r="S9" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1641,38 +1641,38 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127122519</v>
+        <v>127122563</v>
       </c>
       <c r="B10" t="n">
-        <v>57817</v>
+        <v>5176</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>100526</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1681,13 +1681,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>654594</v>
+        <v>654600</v>
       </c>
       <c r="R10" t="n">
-        <v>6648065</v>
+        <v>6648068</v>
       </c>
       <c r="S10" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>

--- a/artfynd/A 25651-2025 artfynd.xlsx
+++ b/artfynd/A 25651-2025 artfynd.xlsx
@@ -1184,7 +1184,7 @@
         <v>127122269</v>
       </c>
       <c r="B6" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>127122952</v>
       </c>
       <c r="B8" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1529,38 +1529,38 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127122519</v>
+        <v>127122563</v>
       </c>
       <c r="B9" t="n">
-        <v>57817</v>
+        <v>5176</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>100526</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1569,13 +1569,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>654594</v>
+        <v>654600</v>
       </c>
       <c r="R9" t="n">
-        <v>6648065</v>
+        <v>6648068</v>
       </c>
       <c r="S9" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1641,38 +1641,38 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127122563</v>
+        <v>127122519</v>
       </c>
       <c r="B10" t="n">
-        <v>5176</v>
+        <v>57817</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100526</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1681,13 +1681,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>654600</v>
+        <v>654594</v>
       </c>
       <c r="R10" t="n">
-        <v>6648068</v>
+        <v>6648065</v>
       </c>
       <c r="S10" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>

--- a/artfynd/A 25651-2025 artfynd.xlsx
+++ b/artfynd/A 25651-2025 artfynd.xlsx
@@ -1529,38 +1529,38 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127122563</v>
+        <v>127122519</v>
       </c>
       <c r="B9" t="n">
-        <v>5176</v>
+        <v>57817</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100526</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1569,13 +1569,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>654600</v>
+        <v>654594</v>
       </c>
       <c r="R9" t="n">
-        <v>6648068</v>
+        <v>6648065</v>
       </c>
       <c r="S9" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1641,38 +1641,38 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127122519</v>
+        <v>127122563</v>
       </c>
       <c r="B10" t="n">
-        <v>57817</v>
+        <v>5176</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>100526</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1681,13 +1681,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>654594</v>
+        <v>654600</v>
       </c>
       <c r="R10" t="n">
-        <v>6648065</v>
+        <v>6648068</v>
       </c>
       <c r="S10" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>

--- a/artfynd/A 25651-2025 artfynd.xlsx
+++ b/artfynd/A 25651-2025 artfynd.xlsx
@@ -1529,38 +1529,38 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127122519</v>
+        <v>127122563</v>
       </c>
       <c r="B9" t="n">
-        <v>57817</v>
+        <v>5176</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>100526</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1569,13 +1569,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>654594</v>
+        <v>654600</v>
       </c>
       <c r="R9" t="n">
-        <v>6648065</v>
+        <v>6648068</v>
       </c>
       <c r="S9" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1641,38 +1641,38 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127122563</v>
+        <v>127122519</v>
       </c>
       <c r="B10" t="n">
-        <v>5176</v>
+        <v>57817</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100526</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1681,13 +1681,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>654600</v>
+        <v>654594</v>
       </c>
       <c r="R10" t="n">
-        <v>6648068</v>
+        <v>6648065</v>
       </c>
       <c r="S10" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>

--- a/artfynd/A 25651-2025 artfynd.xlsx
+++ b/artfynd/A 25651-2025 artfynd.xlsx
@@ -1184,7 +1184,7 @@
         <v>127122269</v>
       </c>
       <c r="B6" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>127122952</v>
       </c>
       <c r="B8" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 25651-2025 artfynd.xlsx
+++ b/artfynd/A 25651-2025 artfynd.xlsx
@@ -1184,7 +1184,7 @@
         <v>127122269</v>
       </c>
       <c r="B6" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
         <v>127122439</v>
       </c>
       <c r="B7" t="n">
-        <v>5196</v>
+        <v>5197</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>127122952</v>
       </c>
       <c r="B8" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1529,38 +1529,38 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127122519</v>
+        <v>127122563</v>
       </c>
       <c r="B9" t="n">
-        <v>57817</v>
+        <v>5177</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>100526</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1569,13 +1569,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>654594</v>
+        <v>654600</v>
       </c>
       <c r="R9" t="n">
-        <v>6648065</v>
+        <v>6648068</v>
       </c>
       <c r="S9" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1641,38 +1641,38 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127122563</v>
+        <v>127122519</v>
       </c>
       <c r="B10" t="n">
-        <v>5176</v>
+        <v>57821</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100526</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1681,13 +1681,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>654600</v>
+        <v>654594</v>
       </c>
       <c r="R10" t="n">
-        <v>6648068</v>
+        <v>6648065</v>
       </c>
       <c r="S10" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>

--- a/artfynd/A 25651-2025 artfynd.xlsx
+++ b/artfynd/A 25651-2025 artfynd.xlsx
@@ -1529,38 +1529,38 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127122563</v>
+        <v>127122519</v>
       </c>
       <c r="B9" t="n">
-        <v>5177</v>
+        <v>57821</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100526</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1569,13 +1569,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>654600</v>
+        <v>654594</v>
       </c>
       <c r="R9" t="n">
-        <v>6648068</v>
+        <v>6648065</v>
       </c>
       <c r="S9" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1641,38 +1641,38 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127122519</v>
+        <v>127122563</v>
       </c>
       <c r="B10" t="n">
-        <v>57821</v>
+        <v>5177</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>100526</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1681,13 +1681,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>654594</v>
+        <v>654600</v>
       </c>
       <c r="R10" t="n">
-        <v>6648065</v>
+        <v>6648068</v>
       </c>
       <c r="S10" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>

--- a/artfynd/A 25651-2025 artfynd.xlsx
+++ b/artfynd/A 25651-2025 artfynd.xlsx
@@ -1184,7 +1184,7 @@
         <v>127122269</v>
       </c>
       <c r="B6" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>127122952</v>
       </c>
       <c r="B8" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 25651-2025 artfynd.xlsx
+++ b/artfynd/A 25651-2025 artfynd.xlsx
@@ -1529,38 +1529,38 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127122519</v>
+        <v>127122563</v>
       </c>
       <c r="B9" t="n">
-        <v>57821</v>
+        <v>5177</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>100526</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1569,13 +1569,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>654594</v>
+        <v>654600</v>
       </c>
       <c r="R9" t="n">
-        <v>6648065</v>
+        <v>6648068</v>
       </c>
       <c r="S9" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1641,38 +1641,38 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127122563</v>
+        <v>127122519</v>
       </c>
       <c r="B10" t="n">
-        <v>5177</v>
+        <v>57821</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100526</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1681,13 +1681,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>654600</v>
+        <v>654594</v>
       </c>
       <c r="R10" t="n">
-        <v>6648068</v>
+        <v>6648065</v>
       </c>
       <c r="S10" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>

--- a/artfynd/A 25651-2025 artfynd.xlsx
+++ b/artfynd/A 25651-2025 artfynd.xlsx
@@ -1184,7 +1184,7 @@
         <v>127122269</v>
       </c>
       <c r="B6" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>127122952</v>
       </c>
       <c r="B8" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1644,7 +1644,7 @@
         <v>127122519</v>
       </c>
       <c r="B10" t="n">
-        <v>57821</v>
+        <v>57823</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 25651-2025 artfynd.xlsx
+++ b/artfynd/A 25651-2025 artfynd.xlsx
@@ -1184,7 +1184,7 @@
         <v>127122269</v>
       </c>
       <c r="B6" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>127122952</v>
       </c>
       <c r="B8" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1529,38 +1529,38 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127122563</v>
+        <v>127122519</v>
       </c>
       <c r="B9" t="n">
-        <v>5177</v>
+        <v>57823</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100526</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1569,13 +1569,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>654600</v>
+        <v>654594</v>
       </c>
       <c r="R9" t="n">
-        <v>6648068</v>
+        <v>6648065</v>
       </c>
       <c r="S9" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1641,38 +1641,38 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127122519</v>
+        <v>127122563</v>
       </c>
       <c r="B10" t="n">
-        <v>57823</v>
+        <v>5177</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>100526</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1681,13 +1681,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>654594</v>
+        <v>654600</v>
       </c>
       <c r="R10" t="n">
-        <v>6648065</v>
+        <v>6648068</v>
       </c>
       <c r="S10" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>

--- a/artfynd/A 25651-2025 artfynd.xlsx
+++ b/artfynd/A 25651-2025 artfynd.xlsx
@@ -1184,7 +1184,7 @@
         <v>127122269</v>
       </c>
       <c r="B6" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>127122952</v>
       </c>
       <c r="B8" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1532,7 +1532,7 @@
         <v>127122519</v>
       </c>
       <c r="B9" t="n">
-        <v>57823</v>
+        <v>57826</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 25651-2025 artfynd.xlsx
+++ b/artfynd/A 25651-2025 artfynd.xlsx
@@ -1184,7 +1184,7 @@
         <v>127122269</v>
       </c>
       <c r="B6" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>127122952</v>
       </c>
       <c r="B8" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1532,7 +1532,7 @@
         <v>127122519</v>
       </c>
       <c r="B9" t="n">
-        <v>57826</v>
+        <v>57832</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 25651-2025 artfynd.xlsx
+++ b/artfynd/A 25651-2025 artfynd.xlsx
@@ -1529,38 +1529,38 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127122519</v>
+        <v>127122563</v>
       </c>
       <c r="B9" t="n">
-        <v>57832</v>
+        <v>5177</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>100526</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1569,13 +1569,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>654594</v>
+        <v>654600</v>
       </c>
       <c r="R9" t="n">
-        <v>6648065</v>
+        <v>6648068</v>
       </c>
       <c r="S9" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1641,38 +1641,38 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127122563</v>
+        <v>127122519</v>
       </c>
       <c r="B10" t="n">
-        <v>5177</v>
+        <v>57832</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100526</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1681,13 +1681,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>654600</v>
+        <v>654594</v>
       </c>
       <c r="R10" t="n">
-        <v>6648068</v>
+        <v>6648065</v>
       </c>
       <c r="S10" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>

--- a/artfynd/A 25651-2025 artfynd.xlsx
+++ b/artfynd/A 25651-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1751,6 +1751,1307 @@
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>129722224</v>
+      </c>
+      <c r="B11" t="n">
+        <v>97014</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>53</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Tomta, Upl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>654363</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6647994</v>
+      </c>
+      <c r="S11" t="n">
+        <v>15</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>129722222</v>
+      </c>
+      <c r="B12" t="n">
+        <v>97014</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>53</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Tomta, Upl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>654421</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6647955</v>
+      </c>
+      <c r="S12" t="n">
+        <v>15</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>129722230</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57732</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Tomta, Upl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>654593</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6648058</v>
+      </c>
+      <c r="S13" t="n">
+        <v>15</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Hackmärken</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>129722221</v>
+      </c>
+      <c r="B14" t="n">
+        <v>97014</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>53</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Tomta, Upl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>654414</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6647974</v>
+      </c>
+      <c r="S14" t="n">
+        <v>15</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>129722238</v>
+      </c>
+      <c r="B15" t="n">
+        <v>98768</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Tomta, Upl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>654633</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6648049</v>
+      </c>
+      <c r="S15" t="n">
+        <v>15</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>10 buketter</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>129722241</v>
+      </c>
+      <c r="B16" t="n">
+        <v>100957</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Tomta, Upl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>654395</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6648021</v>
+      </c>
+      <c r="S16" t="n">
+        <v>15</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>129722228</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57732</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Tomta, Upl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>654431</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6647983</v>
+      </c>
+      <c r="S17" t="n">
+        <v>15</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Hackmärken</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>129722232</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57732</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Tomta, Upl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>654327</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6647956</v>
+      </c>
+      <c r="S18" t="n">
+        <v>15</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Hackmärken</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>129722229</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57732</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Tomta, Upl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>654364</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6648034</v>
+      </c>
+      <c r="S19" t="n">
+        <v>15</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Hackmärken</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>129722223</v>
+      </c>
+      <c r="B20" t="n">
+        <v>97014</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>53</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Tomta, Upl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>654383</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6647948</v>
+      </c>
+      <c r="S20" t="n">
+        <v>15</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>10 dm2</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>129722233</v>
+      </c>
+      <c r="B21" t="n">
+        <v>92907</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Tomta, Upl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>654575</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6648055</v>
+      </c>
+      <c r="S21" t="n">
+        <v>15</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>5 fruktkroppar</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>129722225</v>
+      </c>
+      <c r="B22" t="n">
+        <v>97014</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>53</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Tomta, Upl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>654370</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6647970</v>
+      </c>
+      <c r="S22" t="n">
+        <v>15</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>129722236</v>
+      </c>
+      <c r="B23" t="n">
+        <v>98768</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Tomta, Upl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>654427</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6647986</v>
+      </c>
+      <c r="S23" t="n">
+        <v>15</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>15 buketter</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 25651-2025 artfynd.xlsx
+++ b/artfynd/A 25651-2025 artfynd.xlsx
@@ -1756,7 +1756,7 @@
         <v>129722224</v>
       </c>
       <c r="B11" t="n">
-        <v>97014</v>
+        <v>97015</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1853,7 +1853,7 @@
         <v>129722222</v>
       </c>
       <c r="B12" t="n">
-        <v>97014</v>
+        <v>97015</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1950,7 +1950,7 @@
         <v>129722230</v>
       </c>
       <c r="B13" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2052,7 +2052,7 @@
         <v>129722221</v>
       </c>
       <c r="B14" t="n">
-        <v>97014</v>
+        <v>97015</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         <v>129722238</v>
       </c>
       <c r="B15" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>129722241</v>
       </c>
       <c r="B16" t="n">
-        <v>100957</v>
+        <v>100958</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>129722228</v>
       </c>
       <c r="B17" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2450,7 +2450,7 @@
         <v>129722232</v>
       </c>
       <c r="B18" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2552,7 +2552,7 @@
         <v>129722229</v>
       </c>
       <c r="B19" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2654,7 +2654,7 @@
         <v>129722223</v>
       </c>
       <c r="B20" t="n">
-        <v>97014</v>
+        <v>97015</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2756,7 +2756,7 @@
         <v>129722233</v>
       </c>
       <c r="B21" t="n">
-        <v>92907</v>
+        <v>92908</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2855,32 +2855,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129722225</v>
+        <v>129722236</v>
       </c>
       <c r="B22" t="n">
-        <v>97014</v>
+        <v>98769</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2890,10 +2890,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>654370</v>
+        <v>654427</v>
       </c>
       <c r="R22" t="n">
-        <v>6647970</v>
+        <v>6647986</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2926,6 +2926,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>15 buketter</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2952,32 +2957,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129722236</v>
+        <v>129722225</v>
       </c>
       <c r="B23" t="n">
-        <v>98768</v>
+        <v>97015</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2987,10 +2992,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>654427</v>
+        <v>654370</v>
       </c>
       <c r="R23" t="n">
-        <v>6647986</v>
+        <v>6647970</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3023,11 +3028,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>15 buketter</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 25651-2025 artfynd.xlsx
+++ b/artfynd/A 25651-2025 artfynd.xlsx
@@ -2855,32 +2855,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129722236</v>
+        <v>129722225</v>
       </c>
       <c r="B22" t="n">
-        <v>98769</v>
+        <v>97015</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2890,10 +2890,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>654427</v>
+        <v>654370</v>
       </c>
       <c r="R22" t="n">
-        <v>6647986</v>
+        <v>6647970</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2926,11 +2926,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>15 buketter</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2957,32 +2952,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129722225</v>
+        <v>129722236</v>
       </c>
       <c r="B23" t="n">
-        <v>97015</v>
+        <v>98769</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2992,10 +2987,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>654370</v>
+        <v>654427</v>
       </c>
       <c r="R23" t="n">
-        <v>6647970</v>
+        <v>6647986</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3028,6 +3023,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>15 buketter</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 25651-2025 artfynd.xlsx
+++ b/artfynd/A 25651-2025 artfynd.xlsx
@@ -1756,7 +1756,7 @@
         <v>129722224</v>
       </c>
       <c r="B11" t="n">
-        <v>97015</v>
+        <v>97020</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1853,7 +1853,7 @@
         <v>129722222</v>
       </c>
       <c r="B12" t="n">
-        <v>97015</v>
+        <v>97020</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2052,7 +2052,7 @@
         <v>129722221</v>
       </c>
       <c r="B14" t="n">
-        <v>97015</v>
+        <v>97020</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         <v>129722238</v>
       </c>
       <c r="B15" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>129722241</v>
       </c>
       <c r="B16" t="n">
-        <v>100958</v>
+        <v>100963</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2654,7 +2654,7 @@
         <v>129722223</v>
       </c>
       <c r="B20" t="n">
-        <v>97015</v>
+        <v>97020</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2756,7 +2756,7 @@
         <v>129722233</v>
       </c>
       <c r="B21" t="n">
-        <v>92908</v>
+        <v>92913</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2858,7 +2858,7 @@
         <v>129722225</v>
       </c>
       <c r="B22" t="n">
-        <v>97015</v>
+        <v>97020</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2955,7 +2955,7 @@
         <v>129722236</v>
       </c>
       <c r="B23" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 25651-2025 artfynd.xlsx
+++ b/artfynd/A 25651-2025 artfynd.xlsx
@@ -2049,32 +2049,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129722221</v>
+        <v>129722238</v>
       </c>
       <c r="B14" t="n">
-        <v>97020</v>
+        <v>98774</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2084,10 +2084,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>654414</v>
+        <v>654633</v>
       </c>
       <c r="R14" t="n">
-        <v>6647974</v>
+        <v>6648049</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2120,6 +2120,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>10 buketter</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2146,32 +2151,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129722238</v>
+        <v>129722241</v>
       </c>
       <c r="B15" t="n">
-        <v>98774</v>
+        <v>100963</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2181,10 +2186,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>654633</v>
+        <v>654395</v>
       </c>
       <c r="R15" t="n">
-        <v>6648049</v>
+        <v>6648021</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2217,11 +2222,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>10 buketter</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2248,32 +2248,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129722241</v>
+        <v>129722221</v>
       </c>
       <c r="B16" t="n">
-        <v>100963</v>
+        <v>97020</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222498</v>
+        <v>53</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2283,10 +2283,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>654395</v>
+        <v>654414</v>
       </c>
       <c r="R16" t="n">
-        <v>6648021</v>
+        <v>6647974</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>

--- a/artfynd/A 25651-2025 artfynd.xlsx
+++ b/artfynd/A 25651-2025 artfynd.xlsx
@@ -2049,32 +2049,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129722238</v>
+        <v>129722241</v>
       </c>
       <c r="B14" t="n">
-        <v>98774</v>
+        <v>100963</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2084,10 +2084,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>654633</v>
+        <v>654395</v>
       </c>
       <c r="R14" t="n">
-        <v>6648049</v>
+        <v>6648021</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2120,11 +2120,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>10 buketter</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2151,32 +2146,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129722241</v>
+        <v>129722238</v>
       </c>
       <c r="B15" t="n">
-        <v>100963</v>
+        <v>98774</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2186,10 +2181,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>654395</v>
+        <v>654633</v>
       </c>
       <c r="R15" t="n">
-        <v>6648021</v>
+        <v>6648049</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2222,6 +2217,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>10 buketter</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 25651-2025 artfynd.xlsx
+++ b/artfynd/A 25651-2025 artfynd.xlsx
@@ -2049,32 +2049,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129722241</v>
+        <v>129722221</v>
       </c>
       <c r="B14" t="n">
-        <v>100963</v>
+        <v>97020</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222498</v>
+        <v>53</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2084,10 +2084,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>654395</v>
+        <v>654414</v>
       </c>
       <c r="R14" t="n">
-        <v>6648021</v>
+        <v>6647974</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2248,32 +2248,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129722221</v>
+        <v>129722241</v>
       </c>
       <c r="B16" t="n">
-        <v>97020</v>
+        <v>100963</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>53</v>
+        <v>222498</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2283,10 +2283,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>654414</v>
+        <v>654395</v>
       </c>
       <c r="R16" t="n">
-        <v>6647974</v>
+        <v>6648021</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>

--- a/artfynd/A 25651-2025 artfynd.xlsx
+++ b/artfynd/A 25651-2025 artfynd.xlsx
@@ -1756,7 +1756,7 @@
         <v>129722224</v>
       </c>
       <c r="B11" t="n">
-        <v>97020</v>
+        <v>97024</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1853,7 +1853,7 @@
         <v>129722222</v>
       </c>
       <c r="B12" t="n">
-        <v>97020</v>
+        <v>97024</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2052,7 +2052,7 @@
         <v>129722221</v>
       </c>
       <c r="B14" t="n">
-        <v>97020</v>
+        <v>97024</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2146,32 +2146,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129722238</v>
+        <v>129722241</v>
       </c>
       <c r="B15" t="n">
-        <v>98774</v>
+        <v>100967</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>654633</v>
+        <v>654395</v>
       </c>
       <c r="R15" t="n">
-        <v>6648049</v>
+        <v>6648021</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2217,11 +2217,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>10 buketter</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2248,32 +2243,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129722241</v>
+        <v>129722238</v>
       </c>
       <c r="B16" t="n">
-        <v>100963</v>
+        <v>98778</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2283,10 +2278,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>654395</v>
+        <v>654633</v>
       </c>
       <c r="R16" t="n">
-        <v>6648021</v>
+        <v>6648049</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2319,6 +2314,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>10 buketter</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2654,7 +2654,7 @@
         <v>129722223</v>
       </c>
       <c r="B20" t="n">
-        <v>97020</v>
+        <v>97024</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2756,7 +2756,7 @@
         <v>129722233</v>
       </c>
       <c r="B21" t="n">
-        <v>92913</v>
+        <v>92917</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2858,7 +2858,7 @@
         <v>129722225</v>
       </c>
       <c r="B22" t="n">
-        <v>97020</v>
+        <v>97024</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2955,7 +2955,7 @@
         <v>129722236</v>
       </c>
       <c r="B23" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 25651-2025 artfynd.xlsx
+++ b/artfynd/A 25651-2025 artfynd.xlsx
@@ -1756,7 +1756,7 @@
         <v>129722224</v>
       </c>
       <c r="B11" t="n">
-        <v>97024</v>
+        <v>97026</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1853,7 +1853,7 @@
         <v>129722222</v>
       </c>
       <c r="B12" t="n">
-        <v>97024</v>
+        <v>97026</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2052,7 +2052,7 @@
         <v>129722221</v>
       </c>
       <c r="B14" t="n">
-        <v>97024</v>
+        <v>97026</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2146,32 +2146,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129722241</v>
+        <v>129722238</v>
       </c>
       <c r="B15" t="n">
-        <v>100967</v>
+        <v>98780</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>654395</v>
+        <v>654633</v>
       </c>
       <c r="R15" t="n">
-        <v>6648021</v>
+        <v>6648049</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2217,6 +2217,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>10 buketter</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2243,32 +2248,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129722238</v>
+        <v>129722241</v>
       </c>
       <c r="B16" t="n">
-        <v>98778</v>
+        <v>100969</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2278,10 +2283,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>654633</v>
+        <v>654395</v>
       </c>
       <c r="R16" t="n">
-        <v>6648049</v>
+        <v>6648021</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2314,11 +2319,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>10 buketter</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2654,7 +2654,7 @@
         <v>129722223</v>
       </c>
       <c r="B20" t="n">
-        <v>97024</v>
+        <v>97026</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2756,7 +2756,7 @@
         <v>129722233</v>
       </c>
       <c r="B21" t="n">
-        <v>92917</v>
+        <v>92919</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2855,32 +2855,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129722225</v>
+        <v>129722236</v>
       </c>
       <c r="B22" t="n">
-        <v>97024</v>
+        <v>98780</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2890,10 +2890,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>654370</v>
+        <v>654427</v>
       </c>
       <c r="R22" t="n">
-        <v>6647970</v>
+        <v>6647986</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2926,6 +2926,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>15 buketter</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2952,32 +2957,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129722236</v>
+        <v>129722225</v>
       </c>
       <c r="B23" t="n">
-        <v>98778</v>
+        <v>97026</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2987,10 +2992,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>654427</v>
+        <v>654370</v>
       </c>
       <c r="R23" t="n">
-        <v>6647986</v>
+        <v>6647970</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3023,11 +3028,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>15 buketter</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 25651-2025 artfynd.xlsx
+++ b/artfynd/A 25651-2025 artfynd.xlsx
@@ -1756,7 +1756,7 @@
         <v>129722224</v>
       </c>
       <c r="B11" t="n">
-        <v>97026</v>
+        <v>97036</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1853,7 +1853,7 @@
         <v>129722222</v>
       </c>
       <c r="B12" t="n">
-        <v>97026</v>
+        <v>97036</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2049,32 +2049,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129722221</v>
+        <v>129722238</v>
       </c>
       <c r="B14" t="n">
-        <v>97026</v>
+        <v>98790</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2084,10 +2084,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>654414</v>
+        <v>654633</v>
       </c>
       <c r="R14" t="n">
-        <v>6647974</v>
+        <v>6648049</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2120,6 +2120,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>10 buketter</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2146,32 +2151,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129722238</v>
+        <v>129722241</v>
       </c>
       <c r="B15" t="n">
-        <v>98780</v>
+        <v>100979</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2181,10 +2186,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>654633</v>
+        <v>654395</v>
       </c>
       <c r="R15" t="n">
-        <v>6648049</v>
+        <v>6648021</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2217,11 +2222,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>10 buketter</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2248,32 +2248,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129722241</v>
+        <v>129722221</v>
       </c>
       <c r="B16" t="n">
-        <v>100969</v>
+        <v>97036</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222498</v>
+        <v>53</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2283,10 +2283,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>654395</v>
+        <v>654414</v>
       </c>
       <c r="R16" t="n">
-        <v>6648021</v>
+        <v>6647974</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2654,7 +2654,7 @@
         <v>129722223</v>
       </c>
       <c r="B20" t="n">
-        <v>97026</v>
+        <v>97036</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2855,32 +2855,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129722236</v>
+        <v>129722225</v>
       </c>
       <c r="B22" t="n">
-        <v>98780</v>
+        <v>97036</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2890,10 +2890,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>654427</v>
+        <v>654370</v>
       </c>
       <c r="R22" t="n">
-        <v>6647986</v>
+        <v>6647970</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2926,11 +2926,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>15 buketter</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2957,32 +2952,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129722225</v>
+        <v>129722236</v>
       </c>
       <c r="B23" t="n">
-        <v>97026</v>
+        <v>98790</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2992,10 +2987,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>654370</v>
+        <v>654427</v>
       </c>
       <c r="R23" t="n">
-        <v>6647970</v>
+        <v>6647986</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3028,6 +3023,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>15 buketter</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 25651-2025 artfynd.xlsx
+++ b/artfynd/A 25651-2025 artfynd.xlsx
@@ -2049,32 +2049,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129722238</v>
+        <v>129722221</v>
       </c>
       <c r="B14" t="n">
-        <v>98790</v>
+        <v>97036</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2084,10 +2084,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>654633</v>
+        <v>654414</v>
       </c>
       <c r="R14" t="n">
-        <v>6648049</v>
+        <v>6647974</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2120,11 +2120,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>10 buketter</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2151,32 +2146,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129722241</v>
+        <v>129722238</v>
       </c>
       <c r="B15" t="n">
-        <v>100979</v>
+        <v>98790</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2186,10 +2181,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>654395</v>
+        <v>654633</v>
       </c>
       <c r="R15" t="n">
-        <v>6648021</v>
+        <v>6648049</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2222,6 +2217,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>10 buketter</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2248,32 +2248,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129722221</v>
+        <v>129722241</v>
       </c>
       <c r="B16" t="n">
-        <v>97036</v>
+        <v>100979</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>53</v>
+        <v>222498</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2283,10 +2283,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>654414</v>
+        <v>654395</v>
       </c>
       <c r="R16" t="n">
-        <v>6647974</v>
+        <v>6648021</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2855,32 +2855,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129722225</v>
+        <v>129722236</v>
       </c>
       <c r="B22" t="n">
-        <v>97036</v>
+        <v>98790</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2890,10 +2890,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>654370</v>
+        <v>654427</v>
       </c>
       <c r="R22" t="n">
-        <v>6647970</v>
+        <v>6647986</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2926,6 +2926,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>15 buketter</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2952,32 +2957,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129722236</v>
+        <v>129722225</v>
       </c>
       <c r="B23" t="n">
-        <v>98790</v>
+        <v>97036</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2987,10 +2992,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>654427</v>
+        <v>654370</v>
       </c>
       <c r="R23" t="n">
-        <v>6647986</v>
+        <v>6647970</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3023,11 +3028,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>15 buketter</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 25651-2025 artfynd.xlsx
+++ b/artfynd/A 25651-2025 artfynd.xlsx
@@ -2855,32 +2855,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129722236</v>
+        <v>129722225</v>
       </c>
       <c r="B22" t="n">
-        <v>98790</v>
+        <v>97036</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2890,10 +2890,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>654427</v>
+        <v>654370</v>
       </c>
       <c r="R22" t="n">
-        <v>6647986</v>
+        <v>6647970</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2926,11 +2926,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>15 buketter</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2957,32 +2952,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129722225</v>
+        <v>129722236</v>
       </c>
       <c r="B23" t="n">
-        <v>97036</v>
+        <v>98790</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2992,10 +2987,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>654370</v>
+        <v>654427</v>
       </c>
       <c r="R23" t="n">
-        <v>6647970</v>
+        <v>6647986</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3028,6 +3023,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>15 buketter</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 25651-2025 artfynd.xlsx
+++ b/artfynd/A 25651-2025 artfynd.xlsx
@@ -1753,10 +1753,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129722224</v>
+        <v>129722222</v>
       </c>
       <c r="B11" t="n">
-        <v>97036</v>
+        <v>97040</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1788,10 +1788,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>654363</v>
+        <v>654421</v>
       </c>
       <c r="R11" t="n">
-        <v>6647994</v>
+        <v>6647955</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1850,10 +1850,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129722222</v>
+        <v>129722224</v>
       </c>
       <c r="B12" t="n">
-        <v>97036</v>
+        <v>97040</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1885,10 +1885,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>654421</v>
+        <v>654363</v>
       </c>
       <c r="R12" t="n">
-        <v>6647955</v>
+        <v>6647994</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1950,7 +1950,7 @@
         <v>129722230</v>
       </c>
       <c r="B13" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2049,32 +2049,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129722221</v>
+        <v>129722241</v>
       </c>
       <c r="B14" t="n">
-        <v>97036</v>
+        <v>100983</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>53</v>
+        <v>222498</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2084,10 +2084,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>654414</v>
+        <v>654395</v>
       </c>
       <c r="R14" t="n">
-        <v>6647974</v>
+        <v>6648021</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2146,32 +2146,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129722238</v>
+        <v>129722221</v>
       </c>
       <c r="B15" t="n">
-        <v>98790</v>
+        <v>97040</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>654633</v>
+        <v>654414</v>
       </c>
       <c r="R15" t="n">
-        <v>6648049</v>
+        <v>6647974</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2217,11 +2217,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>10 buketter</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2248,32 +2243,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129722241</v>
+        <v>129722238</v>
       </c>
       <c r="B16" t="n">
-        <v>100979</v>
+        <v>98794</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2283,10 +2278,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>654395</v>
+        <v>654633</v>
       </c>
       <c r="R16" t="n">
-        <v>6648021</v>
+        <v>6648049</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2319,6 +2314,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>10 buketter</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2348,7 +2348,7 @@
         <v>129722228</v>
       </c>
       <c r="B17" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2450,7 +2450,7 @@
         <v>129722232</v>
       </c>
       <c r="B18" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2552,7 +2552,7 @@
         <v>129722229</v>
       </c>
       <c r="B19" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2654,7 +2654,7 @@
         <v>129722223</v>
       </c>
       <c r="B20" t="n">
-        <v>97036</v>
+        <v>97040</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2756,7 +2756,7 @@
         <v>129722233</v>
       </c>
       <c r="B21" t="n">
-        <v>92919</v>
+        <v>92922</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2858,7 +2858,7 @@
         <v>129722225</v>
       </c>
       <c r="B22" t="n">
-        <v>97036</v>
+        <v>97040</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2955,7 +2955,7 @@
         <v>129722236</v>
       </c>
       <c r="B23" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 25651-2025 artfynd.xlsx
+++ b/artfynd/A 25651-2025 artfynd.xlsx
@@ -2855,32 +2855,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129722225</v>
+        <v>129722236</v>
       </c>
       <c r="B22" t="n">
-        <v>97040</v>
+        <v>98794</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2890,10 +2890,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>654370</v>
+        <v>654427</v>
       </c>
       <c r="R22" t="n">
-        <v>6647970</v>
+        <v>6647986</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2926,6 +2926,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>15 buketter</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2952,32 +2957,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129722236</v>
+        <v>129722225</v>
       </c>
       <c r="B23" t="n">
-        <v>98794</v>
+        <v>97040</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2987,10 +2992,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>654427</v>
+        <v>654370</v>
       </c>
       <c r="R23" t="n">
-        <v>6647986</v>
+        <v>6647970</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3023,11 +3028,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>15 buketter</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 25651-2025 artfynd.xlsx
+++ b/artfynd/A 25651-2025 artfynd.xlsx
@@ -1753,10 +1753,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129722222</v>
+        <v>129722224</v>
       </c>
       <c r="B11" t="n">
-        <v>97040</v>
+        <v>97043</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1788,10 +1788,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>654421</v>
+        <v>654363</v>
       </c>
       <c r="R11" t="n">
-        <v>6647955</v>
+        <v>6647994</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1850,10 +1850,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129722224</v>
+        <v>129722222</v>
       </c>
       <c r="B12" t="n">
-        <v>97040</v>
+        <v>97043</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1885,10 +1885,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>654363</v>
+        <v>654421</v>
       </c>
       <c r="R12" t="n">
-        <v>6647994</v>
+        <v>6647955</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1950,7 +1950,7 @@
         <v>129722230</v>
       </c>
       <c r="B13" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2049,32 +2049,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129722241</v>
+        <v>129722238</v>
       </c>
       <c r="B14" t="n">
-        <v>100983</v>
+        <v>98797</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2084,10 +2084,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>654395</v>
+        <v>654633</v>
       </c>
       <c r="R14" t="n">
-        <v>6648021</v>
+        <v>6648049</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2120,6 +2120,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>10 buketter</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2146,32 +2151,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129722221</v>
+        <v>129722241</v>
       </c>
       <c r="B15" t="n">
-        <v>97040</v>
+        <v>100986</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>53</v>
+        <v>222498</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2181,10 +2186,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>654414</v>
+        <v>654395</v>
       </c>
       <c r="R15" t="n">
-        <v>6647974</v>
+        <v>6648021</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2243,32 +2248,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129722238</v>
+        <v>129722221</v>
       </c>
       <c r="B16" t="n">
-        <v>98794</v>
+        <v>97043</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2278,10 +2283,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>654633</v>
+        <v>654414</v>
       </c>
       <c r="R16" t="n">
-        <v>6648049</v>
+        <v>6647974</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2314,11 +2319,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>10 buketter</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2348,7 +2348,7 @@
         <v>129722228</v>
       </c>
       <c r="B17" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2450,7 +2450,7 @@
         <v>129722232</v>
       </c>
       <c r="B18" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2552,7 +2552,7 @@
         <v>129722229</v>
       </c>
       <c r="B19" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2654,7 +2654,7 @@
         <v>129722223</v>
       </c>
       <c r="B20" t="n">
-        <v>97040</v>
+        <v>97043</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2756,7 +2756,7 @@
         <v>129722233</v>
       </c>
       <c r="B21" t="n">
-        <v>92922</v>
+        <v>92925</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2855,32 +2855,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129722236</v>
+        <v>129722225</v>
       </c>
       <c r="B22" t="n">
-        <v>98794</v>
+        <v>97043</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2890,10 +2890,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>654427</v>
+        <v>654370</v>
       </c>
       <c r="R22" t="n">
-        <v>6647986</v>
+        <v>6647970</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2926,11 +2926,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>15 buketter</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2957,32 +2952,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129722225</v>
+        <v>129722236</v>
       </c>
       <c r="B23" t="n">
-        <v>97040</v>
+        <v>98797</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2992,10 +2987,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>654370</v>
+        <v>654427</v>
       </c>
       <c r="R23" t="n">
-        <v>6647970</v>
+        <v>6647986</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3028,6 +3023,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>15 buketter</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 25651-2025 artfynd.xlsx
+++ b/artfynd/A 25651-2025 artfynd.xlsx
@@ -2855,32 +2855,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129722225</v>
+        <v>129722236</v>
       </c>
       <c r="B22" t="n">
-        <v>97043</v>
+        <v>98797</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2890,10 +2890,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>654370</v>
+        <v>654427</v>
       </c>
       <c r="R22" t="n">
-        <v>6647970</v>
+        <v>6647986</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2926,6 +2926,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>15 buketter</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2952,32 +2957,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129722236</v>
+        <v>129722225</v>
       </c>
       <c r="B23" t="n">
-        <v>98797</v>
+        <v>97043</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2987,10 +2992,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>654427</v>
+        <v>654370</v>
       </c>
       <c r="R23" t="n">
-        <v>6647986</v>
+        <v>6647970</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3023,11 +3028,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>15 buketter</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 25651-2025 artfynd.xlsx
+++ b/artfynd/A 25651-2025 artfynd.xlsx
@@ -1756,7 +1756,7 @@
         <v>129722224</v>
       </c>
       <c r="B11" t="n">
-        <v>97043</v>
+        <v>97044</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1853,7 +1853,7 @@
         <v>129722222</v>
       </c>
       <c r="B12" t="n">
-        <v>97043</v>
+        <v>97044</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2049,32 +2049,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129722238</v>
+        <v>129722221</v>
       </c>
       <c r="B14" t="n">
-        <v>98797</v>
+        <v>97044</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2084,10 +2084,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>654633</v>
+        <v>654414</v>
       </c>
       <c r="R14" t="n">
-        <v>6648049</v>
+        <v>6647974</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2120,11 +2120,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>10 buketter</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2154,7 +2149,7 @@
         <v>129722241</v>
       </c>
       <c r="B15" t="n">
-        <v>100986</v>
+        <v>100987</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2248,32 +2243,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129722221</v>
+        <v>129722238</v>
       </c>
       <c r="B16" t="n">
-        <v>97043</v>
+        <v>98798</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2283,10 +2278,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>654414</v>
+        <v>654633</v>
       </c>
       <c r="R16" t="n">
-        <v>6647974</v>
+        <v>6648049</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2319,6 +2314,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>10 buketter</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2654,7 +2654,7 @@
         <v>129722223</v>
       </c>
       <c r="B20" t="n">
-        <v>97043</v>
+        <v>97044</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2756,7 +2756,7 @@
         <v>129722233</v>
       </c>
       <c r="B21" t="n">
-        <v>92925</v>
+        <v>92926</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2858,7 +2858,7 @@
         <v>129722236</v>
       </c>
       <c r="B22" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2960,7 +2960,7 @@
         <v>129722225</v>
       </c>
       <c r="B23" t="n">
-        <v>97043</v>
+        <v>97044</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 25651-2025 artfynd.xlsx
+++ b/artfynd/A 25651-2025 artfynd.xlsx
@@ -1756,7 +1756,7 @@
         <v>129722224</v>
       </c>
       <c r="B11" t="n">
-        <v>97044</v>
+        <v>97061</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1853,7 +1853,7 @@
         <v>129722222</v>
       </c>
       <c r="B12" t="n">
-        <v>97044</v>
+        <v>97061</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2052,7 +2052,7 @@
         <v>129722221</v>
       </c>
       <c r="B14" t="n">
-        <v>97044</v>
+        <v>97061</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2146,32 +2146,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129722241</v>
+        <v>129722238</v>
       </c>
       <c r="B15" t="n">
-        <v>100987</v>
+        <v>98815</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>654395</v>
+        <v>654633</v>
       </c>
       <c r="R15" t="n">
-        <v>6648021</v>
+        <v>6648049</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2217,6 +2217,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>10 buketter</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2243,32 +2248,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129722238</v>
+        <v>129722241</v>
       </c>
       <c r="B16" t="n">
-        <v>98798</v>
+        <v>101004</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2278,10 +2283,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>654633</v>
+        <v>654395</v>
       </c>
       <c r="R16" t="n">
-        <v>6648049</v>
+        <v>6648021</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2314,11 +2319,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>10 buketter</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2654,7 +2654,7 @@
         <v>129722223</v>
       </c>
       <c r="B20" t="n">
-        <v>97044</v>
+        <v>97061</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2756,7 +2756,7 @@
         <v>129722233</v>
       </c>
       <c r="B21" t="n">
-        <v>92926</v>
+        <v>92943</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2855,32 +2855,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129722236</v>
+        <v>129722225</v>
       </c>
       <c r="B22" t="n">
-        <v>98798</v>
+        <v>97061</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2890,10 +2890,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>654427</v>
+        <v>654370</v>
       </c>
       <c r="R22" t="n">
-        <v>6647986</v>
+        <v>6647970</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2926,11 +2926,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>15 buketter</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2957,32 +2952,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129722225</v>
+        <v>129722236</v>
       </c>
       <c r="B23" t="n">
-        <v>97044</v>
+        <v>98815</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2992,10 +2987,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>654370</v>
+        <v>654427</v>
       </c>
       <c r="R23" t="n">
-        <v>6647970</v>
+        <v>6647986</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3028,6 +3023,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>15 buketter</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 25651-2025 artfynd.xlsx
+++ b/artfynd/A 25651-2025 artfynd.xlsx
@@ -1184,7 +1184,7 @@
         <v>127122269</v>
       </c>
       <c r="B6" t="n">
-        <v>98467</v>
+        <v>98436</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
         <v>127122439</v>
       </c>
       <c r="B7" t="n">
-        <v>5197</v>
+        <v>5196</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>127122952</v>
       </c>
       <c r="B8" t="n">
-        <v>98467</v>
+        <v>98436</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1529,38 +1529,38 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127122563</v>
+        <v>127122519</v>
       </c>
       <c r="B9" t="n">
-        <v>5177</v>
+        <v>57817</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100526</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1569,13 +1569,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>654600</v>
+        <v>654594</v>
       </c>
       <c r="R9" t="n">
-        <v>6648068</v>
+        <v>6648065</v>
       </c>
       <c r="S9" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1641,38 +1641,38 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127122519</v>
+        <v>127122563</v>
       </c>
       <c r="B10" t="n">
-        <v>57832</v>
+        <v>5176</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>100526</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1681,13 +1681,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>654594</v>
+        <v>654600</v>
       </c>
       <c r="R10" t="n">
-        <v>6648065</v>
+        <v>6648068</v>
       </c>
       <c r="S10" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>

--- a/artfynd/A 25651-2025 artfynd.xlsx
+++ b/artfynd/A 25651-2025 artfynd.xlsx
@@ -1644,7 +1644,7 @@
         <v>127122519</v>
       </c>
       <c r="B10" t="n">
-        <v>58043</v>
+        <v>58045</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 25651-2025 artfynd.xlsx
+++ b/artfynd/A 25651-2025 artfynd.xlsx
@@ -1644,7 +1644,7 @@
         <v>127122519</v>
       </c>
       <c r="B10" t="n">
-        <v>58045</v>
+        <v>58046</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 25651-2025 artfynd.xlsx
+++ b/artfynd/A 25651-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AY24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3052,6 +3052,112 @@
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>131467099</v>
+      </c>
+      <c r="B24" t="n">
+        <v>99022</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Vintermossröret, Vintermossröret, Upl</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>654592</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6648041</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 25651-2025 artfynd.xlsx
+++ b/artfynd/A 25651-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AY29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>77318303</v>
       </c>
       <c r="B2" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -723,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>654405.8809514265</v>
+        <v>654406</v>
       </c>
       <c r="R2" t="n">
-        <v>6647943.897156163</v>
+        <v>6647944</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,19 +751,9 @@
           <t>2019-04-21</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2019-04-21</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -810,55 +795,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>77318195</v>
+        <v>129722221</v>
       </c>
       <c r="B3" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Tomta, 1,8 km SV-ut, Upl</t>
+          <t>Tomta, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>654333.0944688648</v>
+        <v>654414</v>
       </c>
       <c r="R3" t="n">
-        <v>6648002.06408857</v>
+        <v>6647974</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -882,22 +860,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2019-04-21</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2019-04-21</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,78 +874,66 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Henry Åkerström</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Henry Åkerström, Thorleif Joelson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
-        </is>
-      </c>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>77318194</v>
+        <v>129722222</v>
       </c>
       <c r="B4" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Tomta, 1,8 km SV-ut, Upl</t>
+          <t>Tomta, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>654402.993268434</v>
+        <v>654421</v>
       </c>
       <c r="R4" t="n">
-        <v>6648013.011030598</v>
+        <v>6647955</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1001,22 +957,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2019-04-21</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2019-04-21</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1025,87 +971,66 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Henry Åkerström</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Henry Åkerström, Thorleif Joelson</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
-        </is>
-      </c>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>77318196</v>
+        <v>129722223</v>
       </c>
       <c r="B5" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Tomta, 1,8 km SV-ut, Upl</t>
+          <t>Tomta, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>654416.8498571659</v>
+        <v>654383</v>
       </c>
       <c r="R5" t="n">
-        <v>6648054.22707278</v>
+        <v>6647948</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1129,27 +1054,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2019-04-21</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2019-04-21</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Uppskattat antal.</t>
+          <t>10 dm2</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1158,83 +1073,66 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Henry Åkerström</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Henry Åkerström, Thorleif Joelson</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
-        </is>
-      </c>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127122269</v>
+        <v>129722224</v>
       </c>
       <c r="B6" t="n">
-        <v>98467</v>
+        <v>97358</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Vintermossröret, Vintermossröret, Upl</t>
+          <t>Tomta, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>654599</v>
+        <v>654363</v>
       </c>
       <c r="R6" t="n">
-        <v>6648058</v>
+        <v>6647994</v>
       </c>
       <c r="S6" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1258,22 +1156,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>11:30</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>11:30</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1282,72 +1170,66 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Arvid de Jong</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Arvid de Jong</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127122439</v>
+        <v>129722225</v>
       </c>
       <c r="B7" t="n">
-        <v>5197</v>
+        <v>97358</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>105930</v>
+        <v>53</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Vintermossröret, Vintermossröret, Upl</t>
+          <t>Tomta, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>654599</v>
+        <v>654370</v>
       </c>
       <c r="R7" t="n">
-        <v>6648043</v>
+        <v>6647970</v>
       </c>
       <c r="S7" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1371,22 +1253,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>11:35</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>11:35</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1401,69 +1273,60 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Arvid de Jong</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Arvid de Jong</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127122952</v>
+        <v>131529967</v>
       </c>
       <c r="B8" t="n">
-        <v>98467</v>
+        <v>81312</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>1049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Vintermossröret, Vintermossröret, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>654639</v>
+        <v>654603</v>
       </c>
       <c r="R8" t="n">
-        <v>6648054</v>
+        <v>6648039</v>
       </c>
       <c r="S8" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1487,22 +1350,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>11:35</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>11:35</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1517,22 +1370,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Arvid de Jong</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Arvid de Jong</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127122563</v>
+        <v>129722240</v>
       </c>
       <c r="B9" t="n">
-        <v>5177</v>
+        <v>92564</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1540,42 +1393,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100526</v>
+        <v>1339</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Vintermossröret, Vintermossröret, Upl</t>
+          <t>Tomta, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>654600</v>
+        <v>654666</v>
       </c>
       <c r="R9" t="n">
-        <v>6648068</v>
+        <v>6648046</v>
       </c>
       <c r="S9" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1599,22 +1447,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>11:35</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>11:35</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1629,22 +1467,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Arvid de Jong</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Arvid de Jong</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127122519</v>
+        <v>129722233</v>
       </c>
       <c r="B10" t="n">
-        <v>58063</v>
+        <v>93235</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1652,42 +1490,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>5966</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Vintermossröret, Vintermossröret, Upl</t>
+          <t>Tomta, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>654594</v>
+        <v>654575</v>
       </c>
       <c r="R10" t="n">
-        <v>6648065</v>
+        <v>6648055</v>
       </c>
       <c r="S10" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1711,22 +1544,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>11:35</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>11:35</t>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>5 fruktkroppar</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1741,44 +1569,44 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Arvid de Jong</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Arvid de Jong</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129722222</v>
+        <v>129722228</v>
       </c>
       <c r="B11" t="n">
-        <v>97066</v>
+        <v>57950</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>53</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1788,10 +1616,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>654421</v>
+        <v>654431</v>
       </c>
       <c r="R11" t="n">
-        <v>6647955</v>
+        <v>6647983</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1824,6 +1652,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1850,32 +1683,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129722224</v>
+        <v>129722229</v>
       </c>
       <c r="B12" t="n">
-        <v>97066</v>
+        <v>57950</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>53</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1885,10 +1718,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>654363</v>
+        <v>654364</v>
       </c>
       <c r="R12" t="n">
-        <v>6647994</v>
+        <v>6648034</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1921,6 +1754,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1950,11 +1788,11 @@
         <v>129722230</v>
       </c>
       <c r="B13" t="n">
-        <v>57737</v>
+        <v>57950</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -2049,10 +1887,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129722241</v>
+        <v>129722232</v>
       </c>
       <c r="B14" t="n">
-        <v>101009</v>
+        <v>57950</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2060,21 +1898,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2084,10 +1922,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>654395</v>
+        <v>654327</v>
       </c>
       <c r="R14" t="n">
-        <v>6648021</v>
+        <v>6647956</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2120,6 +1958,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2146,48 +1989,53 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129722221</v>
+        <v>127122563</v>
       </c>
       <c r="B15" t="n">
-        <v>97066</v>
+        <v>5179</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>53</v>
+        <v>100526</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Tomta, Upl</t>
+          <t>Vintermossröret, Vintermossröret, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>654414</v>
+        <v>654600</v>
       </c>
       <c r="R15" t="n">
-        <v>6647974</v>
+        <v>6648068</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2211,12 +2059,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2231,44 +2089,44 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129722238</v>
+        <v>129722239</v>
       </c>
       <c r="B16" t="n">
-        <v>98820</v>
+        <v>5179</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2278,10 +2136,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>654633</v>
+        <v>654622</v>
       </c>
       <c r="R16" t="n">
-        <v>6648049</v>
+        <v>6648099</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2314,11 +2172,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>10 buketter</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2345,10 +2198,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129722228</v>
+        <v>127122519</v>
       </c>
       <c r="B17" t="n">
-        <v>57737</v>
+        <v>58114</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2356,37 +2209,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Tomta, Upl</t>
+          <t>Vintermossröret, Vintermossröret, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>654431</v>
+        <v>654594</v>
       </c>
       <c r="R17" t="n">
-        <v>6647983</v>
+        <v>6648065</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2410,17 +2268,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Hackmärken</t>
+          <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2435,39 +2298,39 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129722232</v>
+        <v>127122439</v>
       </c>
       <c r="B18" t="n">
-        <v>57737</v>
+        <v>5199</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>105930</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2476,19 +2339,24 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Tomta, Upl</t>
+          <t>Vintermossröret, Vintermossröret, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>654327</v>
+        <v>654599</v>
       </c>
       <c r="R18" t="n">
-        <v>6647956</v>
+        <v>6648043</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2512,17 +2380,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Hackmärken</t>
+          <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2537,60 +2410,62 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129722229</v>
+        <v>77318194</v>
       </c>
       <c r="B19" t="n">
-        <v>57737</v>
+        <v>99118</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Tomta, Upl</t>
+          <t>Tomta, 1,8 km SV-ut, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>654364</v>
+        <v>654403</v>
       </c>
       <c r="R19" t="n">
-        <v>6648034</v>
+        <v>6648013</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2614,17 +2489,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2019-04-21</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Hackmärken</t>
+          <t>2019-04-21</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2633,66 +2503,82 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Henry Åkerström</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr"/>
+          <t>Henry Åkerström, Thorleif Joelson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129722223</v>
+        <v>77318196</v>
       </c>
       <c r="B20" t="n">
-        <v>97066</v>
+        <v>99118</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Tomta, Upl</t>
+          <t>Tomta, 1,8 km SV-ut, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>654383</v>
+        <v>654417</v>
       </c>
       <c r="R20" t="n">
-        <v>6647948</v>
+        <v>6648054</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2716,17 +2602,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2019-04-21</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2019-04-21</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>10 dm2</t>
+          <t>Uppskattat antal.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2735,66 +2621,83 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Henry Åkerström</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr"/>
+          <t>Henry Åkerström, Thorleif Joelson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129722233</v>
+        <v>127122269</v>
       </c>
       <c r="B21" t="n">
-        <v>92948</v>
+        <v>99118</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5966</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Tomta, Upl</t>
+          <t>Vintermossröret, Vintermossröret, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>654575</v>
+        <v>654599</v>
       </c>
       <c r="R21" t="n">
-        <v>6648055</v>
+        <v>6648058</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2818,17 +2721,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>5 fruktkroppar</t>
+          <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2837,66 +2745,76 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129722225</v>
+        <v>127122952</v>
       </c>
       <c r="B22" t="n">
-        <v>97066</v>
+        <v>99118</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Tomta, Upl</t>
+          <t>Vintermossröret, Vintermossröret, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>654370</v>
+        <v>654639</v>
       </c>
       <c r="R22" t="n">
-        <v>6647970</v>
+        <v>6648054</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2920,12 +2838,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2940,12 +2868,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -2955,7 +2883,7 @@
         <v>129722236</v>
       </c>
       <c r="B23" t="n">
-        <v>98820</v>
+        <v>99118</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3054,10 +2982,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131467099</v>
+        <v>129722238</v>
       </c>
       <c r="B24" t="n">
-        <v>99054</v>
+        <v>99118</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3082,29 +3010,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Vintermossröret, Vintermossröret, Upl</t>
+          <t>Tomta, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>654592</v>
+        <v>654633</v>
       </c>
       <c r="R24" t="n">
-        <v>6648041</v>
+        <v>6648049</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3128,12 +3047,17 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>10 buketter</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3148,57 +3072,66 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131529967</v>
+        <v>131467099</v>
       </c>
       <c r="B25" t="n">
-        <v>81261</v>
+        <v>99118</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1049</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Vintermossröret, Vintermossröret, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>654603</v>
+        <v>654592</v>
       </c>
       <c r="R25" t="n">
-        <v>6648039</v>
+        <v>6648041</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3225,12 +3158,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3254,6 +3187,416 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>77318195</v>
+      </c>
+      <c r="B26" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Tomta, 1,8 km SV-ut, Upl</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>654333</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6648002</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2019-04-21</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2019-04-21</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Henry Åkerström, Thorleif Joelson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>77318193</v>
+      </c>
+      <c r="B27" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Tomta, 1,7 km SV-ut, Upl</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>654572</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6647962</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2019-04-21</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2019-04-21</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Henry Åkerström, Thorleif Joelson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>78260920</v>
+      </c>
+      <c r="B28" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Tomta, 1,8 km SV-ut, Upl</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>654384</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6648065</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2019-06-02</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2019-06-02</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Henry Åkerström, Thorleif Joelson, Jörgen Sjöström</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>129722241</v>
+      </c>
+      <c r="B29" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Tomta, Upl</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>654395</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6648021</v>
+      </c>
+      <c r="S29" t="n">
+        <v>15</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
